--- a/Configs/GameConfig/Datas/weapon.xlsx
+++ b/Configs/GameConfig/Datas/weapon.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R28b63731afb24ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R57757deb621e4b3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -504,7 +504,7 @@
     <x:row r="5">
       <x:c r="A5"/>
       <x:c r="B5" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" t="n">
         <x:v>0</x:v>
@@ -542,7 +542,7 @@
     <x:row r="6">
       <x:c r="A6"/>
       <x:c r="B6" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" t="n">
         <x:v>0</x:v>
@@ -578,7 +578,7 @@
     <x:row r="7">
       <x:c r="A7"/>
       <x:c r="B7" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" t="n">
         <x:v>0</x:v>
@@ -614,7 +614,7 @@
     <x:row r="8">
       <x:c r="A8"/>
       <x:c r="B8" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C8" t="n">
         <x:v>0</x:v>
@@ -650,7 +650,7 @@
     <x:row r="9">
       <x:c r="A9"/>
       <x:c r="B9" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C9" t="n">
         <x:v>0</x:v>
@@ -688,7 +688,7 @@
     <x:row r="10">
       <x:c r="A10"/>
       <x:c r="B10" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" t="n">
         <x:v>0</x:v>
@@ -728,7 +728,7 @@
     <x:row r="11">
       <x:c r="A11"/>
       <x:c r="B11" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" t="n">
         <x:v>0</x:v>
@@ -766,7 +766,7 @@
     <x:row r="12">
       <x:c r="A12"/>
       <x:c r="B12" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" t="n">
         <x:v>0</x:v>
@@ -804,7 +804,7 @@
     <x:row r="13">
       <x:c r="A13"/>
       <x:c r="B13" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C13" t="n">
         <x:v>0</x:v>
@@ -842,7 +842,7 @@
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" t="n">
         <x:v>0</x:v>
@@ -880,7 +880,7 @@
     <x:row r="15">
       <x:c r="A15"/>
       <x:c r="B15" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" t="n">
         <x:v>1</x:v>
@@ -918,7 +918,7 @@
     <x:row r="16">
       <x:c r="A16"/>
       <x:c r="B16" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C16" t="n">
         <x:v>1</x:v>
@@ -954,7 +954,7 @@
     <x:row r="17">
       <x:c r="A17"/>
       <x:c r="B17" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C17" t="n">
         <x:v>1</x:v>
@@ -990,7 +990,7 @@
     <x:row r="18">
       <x:c r="A18"/>
       <x:c r="B18" t="n">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" t="n">
         <x:v>1</x:v>
@@ -1026,7 +1026,7 @@
     <x:row r="19">
       <x:c r="A19"/>
       <x:c r="B19" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C19" t="n">
         <x:v>1</x:v>
@@ -1062,7 +1062,7 @@
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" t="n">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" t="n">
         <x:v>1</x:v>
@@ -1100,7 +1100,7 @@
     <x:row r="21">
       <x:c r="A21"/>
       <x:c r="B21" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" t="n">
         <x:v>1</x:v>
@@ -1138,7 +1138,7 @@
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" t="n">
         <x:v>1</x:v>
@@ -1178,7 +1178,7 @@
     <x:row r="23">
       <x:c r="A23"/>
       <x:c r="B23" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" t="n">
         <x:v>1</x:v>
@@ -1218,7 +1218,7 @@
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" t="n">
         <x:v>1</x:v>
@@ -1258,7 +1258,7 @@
     <x:row r="25">
       <x:c r="A25"/>
       <x:c r="B25" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C25" t="n">
         <x:v>2</x:v>
@@ -1296,7 +1296,7 @@
     <x:row r="26">
       <x:c r="A26"/>
       <x:c r="B26" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C26" t="n">
         <x:v>2</x:v>
@@ -1332,7 +1332,7 @@
     <x:row r="27">
       <x:c r="A27"/>
       <x:c r="B27" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" t="n">
         <x:v>2</x:v>
@@ -1368,7 +1368,7 @@
     <x:row r="28">
       <x:c r="A28"/>
       <x:c r="B28" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C28" t="n">
         <x:v>2</x:v>
@@ -1404,7 +1404,7 @@
     <x:row r="29">
       <x:c r="A29"/>
       <x:c r="B29" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C29" t="n">
         <x:v>2</x:v>
@@ -1440,7 +1440,7 @@
     <x:row r="30">
       <x:c r="A30"/>
       <x:c r="B30" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C30" t="n">
         <x:v>2</x:v>
@@ -1476,7 +1476,7 @@
     <x:row r="31">
       <x:c r="A31"/>
       <x:c r="B31" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C31" t="n">
         <x:v>2</x:v>
@@ -1514,7 +1514,7 @@
     <x:row r="32">
       <x:c r="A32"/>
       <x:c r="B32" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" t="n">
         <x:v>2</x:v>
@@ -1554,7 +1554,7 @@
     <x:row r="33">
       <x:c r="A33"/>
       <x:c r="B33" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C33" t="n">
         <x:v>2</x:v>
@@ -1592,7 +1592,7 @@
     <x:row r="34">
       <x:c r="A34"/>
       <x:c r="B34" t="n">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C34" t="n">
         <x:v>2</x:v>
@@ -1632,7 +1632,7 @@
     <x:row r="35">
       <x:c r="A35"/>
       <x:c r="B35" t="n">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C35" t="n">
         <x:v>2</x:v>
@@ -1672,7 +1672,7 @@
     <x:row r="36">
       <x:c r="A36"/>
       <x:c r="B36" t="n">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C36" t="n">
         <x:v>3</x:v>
@@ -1710,7 +1710,7 @@
     <x:row r="37">
       <x:c r="A37"/>
       <x:c r="B37" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C37" t="n">
         <x:v>3</x:v>
@@ -1746,7 +1746,7 @@
     <x:row r="38">
       <x:c r="A38"/>
       <x:c r="B38" t="n">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C38" t="n">
         <x:v>3</x:v>
@@ -1782,7 +1782,7 @@
     <x:row r="39">
       <x:c r="A39"/>
       <x:c r="B39" t="n">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C39" t="n">
         <x:v>3</x:v>
@@ -1818,7 +1818,7 @@
     <x:row r="40">
       <x:c r="A40"/>
       <x:c r="B40" t="n">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C40" t="n">
         <x:v>3</x:v>
@@ -1854,7 +1854,7 @@
     <x:row r="41">
       <x:c r="A41"/>
       <x:c r="B41" t="n">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C41" t="n">
         <x:v>3</x:v>
@@ -1892,7 +1892,7 @@
     <x:row r="42">
       <x:c r="A42"/>
       <x:c r="B42" t="n">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C42" t="n">
         <x:v>3</x:v>
@@ -1932,7 +1932,7 @@
     <x:row r="43">
       <x:c r="A43"/>
       <x:c r="B43" t="n">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C43" t="n">
         <x:v>3</x:v>
@@ -1972,7 +1972,7 @@
     <x:row r="44">
       <x:c r="A44"/>
       <x:c r="B44" t="n">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" t="n">
         <x:v>3</x:v>
@@ -2010,7 +2010,7 @@
     <x:row r="45">
       <x:c r="A45"/>
       <x:c r="B45" t="n">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C45" t="n">
         <x:v>3</x:v>
@@ -2048,7 +2048,7 @@
     <x:row r="46">
       <x:c r="A46"/>
       <x:c r="B46" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C46" t="n">
         <x:v>3</x:v>
@@ -2086,7 +2086,7 @@
     <x:row r="47">
       <x:c r="A47"/>
       <x:c r="B47" t="n">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C47" t="n">
         <x:v>3</x:v>
@@ -2124,7 +2124,7 @@
     <x:row r="48">
       <x:c r="A48"/>
       <x:c r="B48" t="n">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C48" t="n">
         <x:v>3</x:v>
